--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/NORTH_DAKOTA_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/NORTH_DAKOTA_2020.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C8">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C43">
